--- a/stick-world/config/excel/平衡变量.xlsx
+++ b/stick-world/config/excel/平衡变量.xlsx
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
         <v>200</v>
-      </c>
-      <c r="D12" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1000</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>

--- a/stick-world/config/excel/平衡变量.xlsx
+++ b/stick-world/config/excel/平衡变量.xlsx
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
